--- a/public/Book1.xlsx
+++ b/public/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\Projects\sams\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E0D7E9-73F2-4511-B073-25A4D3E3C206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE227C3-C120-417F-AD7B-0BE9B338A973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4447BBC0-5A1D-46AF-92AC-9B6E674B6B42}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>Liam</t>
   </si>
@@ -132,7 +132,16 @@
     <t>Aaron@tester</t>
   </si>
   <si>
-    <t>TEST SECTION</t>
+    <t>section</t>
+  </si>
+  <si>
+    <t>Section A</t>
+  </si>
+  <si>
+    <t>Section B</t>
+  </si>
+  <si>
+    <t>Section C</t>
   </si>
 </sst>
 </file>
@@ -496,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07D80247-F523-4358-9FC4-5E7E8FB23CE1}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -509,310 +518,365 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" t="str">
-        <f>_xlfn.CONCAT(C7, "@tester")</f>
-        <v>Liam@tester</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="str">
-        <f t="shared" ref="D8:D13" si="0">_xlfn.CONCAT(C8, "@tester")</f>
-        <v>Olivia@tester</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
+        <f>_xlfn.CONCAT(C8, "@tester")</f>
+        <v>Liam@tester</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" ref="D9:D14" si="0">_xlfn.CONCAT(C9, "@tester")</f>
+        <v>Olivia@tester</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D10" t="str">
         <f t="shared" si="0"/>
         <v>Noah@tester</v>
       </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
         <v>3</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D11" t="str">
         <f t="shared" si="0"/>
         <v>Emma@tester</v>
       </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
         <v>4</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D12" t="str">
         <f t="shared" si="0"/>
         <v>Oliver@tester</v>
       </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D13" t="str">
         <f t="shared" si="0"/>
         <v>Ava@tester</v>
       </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
         <v>6</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D14" t="str">
         <f t="shared" si="0"/>
         <v>Elijah@tester</v>
       </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="str">
-        <f t="shared" ref="D20:D30" si="1">_xlfn.CONCAT(C20, "@tester")</f>
-        <v>Mateo@tester</v>
-      </c>
-      <c r="E20" t="s">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" t="str">
-        <f t="shared" si="1"/>
-        <v>Isabella@tester</v>
-      </c>
-      <c r="E21" t="s">
-        <v>32</v>
+      <c r="B21" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" t="str">
-        <f t="shared" si="1"/>
-        <v>Lucas@tester</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
+        <f t="shared" ref="D22:D32" si="1">_xlfn.CONCAT(C22, "@tester")</f>
+        <v>Mateo@tester</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" t="str">
         <f t="shared" si="1"/>
-        <v>Mia@tester</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
+        <v>Isabella@tester</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" t="str">
         <f t="shared" si="1"/>
-        <v>Levi@tester</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
+        <v>Lucas@tester</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D25" t="str">
         <f t="shared" si="1"/>
-        <v>Charlotte@tester</v>
-      </c>
-      <c r="E25" t="s">
-        <v>32</v>
+        <v>Mia@tester</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D26" t="str">
         <f t="shared" si="1"/>
-        <v>Ezra@tester</v>
-      </c>
-      <c r="E26" t="s">
-        <v>32</v>
+        <v>Levi@tester</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D27" t="str">
         <f t="shared" si="1"/>
-        <v>Amelia@tester</v>
-      </c>
-      <c r="E27" t="s">
-        <v>32</v>
+        <v>Charlotte@tester</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D28" t="str">
         <f t="shared" si="1"/>
-        <v>Asher@tester</v>
-      </c>
-      <c r="E28" t="s">
-        <v>32</v>
+        <v>Ezra@tester</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D29" t="str">
         <f t="shared" si="1"/>
-        <v>Harper@tester</v>
-      </c>
-      <c r="E29" t="s">
-        <v>32</v>
+        <v>Amelia@tester</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="1"/>
+        <v>Asher@tester</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="1"/>
+        <v>Harper@tester</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
         <v>17</v>
       </c>
-      <c r="D30" t="str">
+      <c r="D32" t="str">
         <f t="shared" si="1"/>
         <v>Leo@tester</v>
       </c>
-      <c r="E30" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" ref="D40:D44" si="2">_xlfn.CONCAT(C40, "@tester")</f>
+        <v>Mateo@tester</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="2"/>
+        <v>Isabella@tester</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="2"/>
+        <v>Lucas@tester</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="2"/>
+        <v>Mia@tester</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="2"/>
+        <v>Levi@tester</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{01775EDC-799E-491E-B3E6-D7D1C398D84B}"/>
-    <hyperlink ref="C15" r:id="rId2" xr:uid="{DEEEB2B1-48B5-43D2-A378-CE6E68FDE495}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{01775EDC-799E-491E-B3E6-D7D1C398D84B}"/>
+    <hyperlink ref="C17" r:id="rId2" xr:uid="{DEEEB2B1-48B5-43D2-A378-CE6E68FDE495}"/>
+    <hyperlink ref="C35" r:id="rId3" xr:uid="{623C63B0-392B-4B44-8D6C-5910C6DC45E0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/Book1.xlsx
+++ b/public/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\Projects\sams\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE227C3-C120-417F-AD7B-0BE9B338A973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C9FB72-878E-4E9B-86E7-20C2972EAAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{4447BBC0-5A1D-46AF-92AC-9B6E674B6B42}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="45">
   <si>
     <t>Liam</t>
   </si>
@@ -142,6 +142,33 @@
   </si>
   <si>
     <t>Section C</t>
+  </si>
+  <si>
+    <t>Julia</t>
+  </si>
+  <si>
+    <t>Julia@parent</t>
+  </si>
+  <si>
+    <t>classroom</t>
+  </si>
+  <si>
+    <t>R102</t>
+  </si>
+  <si>
+    <t>E512</t>
+  </si>
+  <si>
+    <t>Katie</t>
+  </si>
+  <si>
+    <t>Katie@parent</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
+    <t>Felix@parent</t>
   </si>
 </sst>
 </file>
@@ -505,18 +532,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07D80247-F523-4358-9FC4-5E7E8FB23CE1}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>32</v>
       </c>
@@ -524,359 +553,562 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
         <v>0</v>
       </c>
-      <c r="D8" t="str">
-        <f>_xlfn.CONCAT(C8, "@tester")</f>
+      <c r="D9" t="str">
+        <f>_xlfn.CONCAT(C9, "@tester")</f>
         <v>Liam@tester</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
         <v>1</v>
       </c>
-      <c r="D9" t="str">
-        <f t="shared" ref="D9:D14" si="0">_xlfn.CONCAT(C9, "@tester")</f>
+      <c r="D10" t="str">
+        <f t="shared" ref="D10:D15" si="0">_xlfn.CONCAT(C10, "@tester")</f>
         <v>Olivia@tester</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
         <v>2</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D11" t="str">
         <f t="shared" si="0"/>
         <v>Noah@tester</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
         <v>3</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D12" t="str">
         <f t="shared" si="0"/>
         <v>Emma@tester</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
         <v>4</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D13" t="str">
         <f t="shared" si="0"/>
         <v>Oliver@tester</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D14" t="str">
         <f t="shared" si="0"/>
         <v>Ava@tester</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
         <v>6</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D15" t="str">
         <f t="shared" si="0"/>
         <v>Elijah@tester</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>32</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
         <v>7</v>
       </c>
-      <c r="D22" t="str">
-        <f t="shared" ref="D22:D32" si="1">_xlfn.CONCAT(C22, "@tester")</f>
+      <c r="D24" t="str">
+        <f t="shared" ref="D24:D34" si="1">_xlfn.CONCAT(C24, "@tester")</f>
         <v>Mateo@tester</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
+      <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
         <v>8</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D25" t="str">
         <f t="shared" si="1"/>
         <v>Isabella@tester</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
+      <c r="E25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="D24" t="str">
+      <c r="D26" t="str">
         <f t="shared" si="1"/>
         <v>Lucas@tester</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D27" t="str">
         <f t="shared" si="1"/>
         <v>Mia@tester</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C26" t="s">
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
         <v>11</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D28" t="str">
         <f t="shared" si="1"/>
         <v>Levi@tester</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C27" t="s">
+      <c r="E28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
         <v>12</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D29" t="str">
         <f t="shared" si="1"/>
         <v>Charlotte@tester</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
         <v>13</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D30" t="str">
         <f t="shared" si="1"/>
         <v>Ezra@tester</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
         <v>14</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D31" t="str">
         <f t="shared" si="1"/>
         <v>Amelia@tester</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="D30" t="str">
+      <c r="D32" t="str">
         <f t="shared" si="1"/>
         <v>Asher@tester</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
+      <c r="E32" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
         <v>16</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D33" t="str">
         <f t="shared" si="1"/>
         <v>Harper@tester</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
+      <c r="E33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
         <v>17</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D34" t="str">
         <f t="shared" si="1"/>
         <v>Leo@tester</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="E34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>32</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C38" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C40" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
         <v>7</v>
       </c>
-      <c r="D40" t="str">
-        <f t="shared" ref="D40:D44" si="2">_xlfn.CONCAT(C40, "@tester")</f>
+      <c r="D43" t="str">
+        <f t="shared" ref="D43:D47" si="2">_xlfn.CONCAT(C43, "@tester")</f>
         <v>Mateo@tester</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
+      <c r="E43" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
         <v>8</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D44" t="str">
         <f t="shared" si="2"/>
         <v>Isabella@tester</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C42" t="s">
+      <c r="E44" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
         <v>9</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D45" t="str">
         <f t="shared" si="2"/>
         <v>Lucas@tester</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C43" t="s">
+      <c r="E45" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
         <v>10</v>
       </c>
-      <c r="D43" t="str">
+      <c r="D46" t="str">
         <f t="shared" si="2"/>
         <v>Mia@tester</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C44" t="s">
+      <c r="E46" t="s">
+        <v>41</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
         <v>11</v>
       </c>
-      <c r="D44" t="str">
+      <c r="D47" t="str">
         <f t="shared" si="2"/>
         <v>Levi@tester</v>
       </c>
+      <c r="E47" t="s">
+        <v>41</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F53" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{01775EDC-799E-491E-B3E6-D7D1C398D84B}"/>
-    <hyperlink ref="C17" r:id="rId2" xr:uid="{DEEEB2B1-48B5-43D2-A378-CE6E68FDE495}"/>
-    <hyperlink ref="C35" r:id="rId3" xr:uid="{623C63B0-392B-4B44-8D6C-5910C6DC45E0}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{01775EDC-799E-491E-B3E6-D7D1C398D84B}"/>
+    <hyperlink ref="C19" r:id="rId2" xr:uid="{DEEEB2B1-48B5-43D2-A378-CE6E68FDE495}"/>
+    <hyperlink ref="C38" r:id="rId3" xr:uid="{623C63B0-392B-4B44-8D6C-5910C6DC45E0}"/>
+    <hyperlink ref="F9" r:id="rId4" xr:uid="{1867BFBC-8A6E-4367-AC7A-DAC367B6D805}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{5E086E3D-2FA1-4F37-8137-C3620F432DB6}"/>
+    <hyperlink ref="F11" r:id="rId6" xr:uid="{6C1EE2F6-8B6B-413A-9B0C-AD8888CB811D}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{83117D30-6F5D-4263-9750-0EFB66211CA1}"/>
+    <hyperlink ref="F13" r:id="rId8" xr:uid="{6D37DE4D-BCBC-465A-AD91-F3C8FCD9F339}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{7302DFAE-FAA3-4D3D-B5F2-E2C8F61CF6CB}"/>
+    <hyperlink ref="F15" r:id="rId10" xr:uid="{D7F67A71-5592-4D93-8B4D-10F8A7653528}"/>
+    <hyperlink ref="F24" r:id="rId11" xr:uid="{3D51D9EF-C698-495A-ACEF-21E3E1284DDC}"/>
+    <hyperlink ref="F25" r:id="rId12" xr:uid="{ACA99B4C-93C8-4034-8897-8449E851908D}"/>
+    <hyperlink ref="F26" r:id="rId13" xr:uid="{149B1850-5AF9-4B5B-AA9A-F813B37C0175}"/>
+    <hyperlink ref="F27" r:id="rId14" xr:uid="{DA036A2F-D737-40C0-A07D-D2D76D86554D}"/>
+    <hyperlink ref="F28" r:id="rId15" xr:uid="{2A24C9E3-38D0-493D-8842-2FBA211BA608}"/>
+    <hyperlink ref="F29" r:id="rId16" xr:uid="{9226935D-D31E-4DD8-AD85-AAB04273C5C2}"/>
+    <hyperlink ref="F30" r:id="rId17" xr:uid="{059D859C-9BA2-49E3-B0EE-CC66598AE702}"/>
+    <hyperlink ref="F31" r:id="rId18" xr:uid="{FB267688-FC14-4337-A7C2-196021F4D2C3}"/>
+    <hyperlink ref="F32" r:id="rId19" xr:uid="{268E9781-3F9C-4228-87B7-473D4FB433CE}"/>
+    <hyperlink ref="F33" r:id="rId20" xr:uid="{D1E66535-0AF4-4DFB-8C1B-7EC0C0E8CD13}"/>
+    <hyperlink ref="F34" r:id="rId21" xr:uid="{A5BCE77A-4DFA-4C3D-9D49-E2FF969DECFF}"/>
+    <hyperlink ref="F43" r:id="rId22" xr:uid="{516AC170-AB28-42F9-835B-C61193ADB62E}"/>
+    <hyperlink ref="F44" r:id="rId23" xr:uid="{728BD8E9-F849-4935-906A-61B8F8E33409}"/>
+    <hyperlink ref="F45" r:id="rId24" xr:uid="{286567F6-C90E-4966-B8BD-8EB276517C34}"/>
+    <hyperlink ref="F46" r:id="rId25" xr:uid="{CDD19AD2-D327-498E-B25C-78A090134B6F}"/>
+    <hyperlink ref="F47" r:id="rId26" xr:uid="{F789F51D-E0BF-4DA9-8F35-6CDE816197A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
